--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123458759</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123458759</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123458759</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123458759</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123458759</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125684775</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>388114</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6611832</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125684775</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21252-2024 artfynd.xlsx
+++ b/artfynd/A 21252-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123458759</v>
+        <v>123697725</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388109</v>
+        <v>388147</v>
       </c>
       <c r="R2" t="n">
-        <v>6611835</v>
+        <v>6611774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,64 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125684775</v>
+        <v>118745853</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>5178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>103</t>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388114</v>
+        <v>388147</v>
       </c>
       <c r="R3" t="n">
-        <v>6611832</v>
+        <v>6611748</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,18 +859,260 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123458759</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>388109</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6611835</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Martinell-Funch</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125684775</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>388114</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6611832</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Lina Lejonberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Lina Lejonberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
